--- a/data/history/SCRAPING_REKAP_SE2026_AMBON_20260731_180524.xlsx
+++ b/data/history/SCRAPING_REKAP_SE2026_AMBON_20260731_180524.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ZULFAA\BPS\Scrapping\monitoring-petugas\data\history\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36125EFE-5BBE-4C59-8B63-D691C8659014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1634E45-E343-48B1-9325-5730C33EDE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20478" uniqueCount="2682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20480" uniqueCount="2682">
   <si>
     <t>userId</t>
   </si>
@@ -94567,6 +94567,9 @@
       <c r="S1361" t="s">
         <v>33</v>
       </c>
+      <c r="T1361" t="s">
+        <v>34</v>
+      </c>
       <c r="U1361" t="s">
         <v>713</v>
       </c>
@@ -94684,6 +94687,9 @@
       </c>
       <c r="S1363" t="s">
         <v>33</v>
+      </c>
+      <c r="T1363" t="s">
+        <v>34</v>
       </c>
       <c r="U1363" t="s">
         <v>713</v>
